--- a/mtil/scripts/reslut_table.xlsx
+++ b/mtil/scripts/reslut_table.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/iiau_hzc/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/iiau_hzc/Documents/Code/MoE-Adapters++/实验结果/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C2231E9-147F-9D4F-89D0-F17A4CEEB4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505EA4A5-1EC1-D540-9820-E5D4E626E865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5540" yWindow="2340" windowWidth="23860" windowHeight="15720" xr2:uid="{BA9F9624-647D-5141-9BF1-6B06BB7E11D0}"/>
+    <workbookView xWindow="5060" yWindow="4020" windowWidth="23860" windowHeight="15720" xr2:uid="{BA9F9624-647D-5141-9BF1-6B06BB7E11D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="14">
   <si>
     <t>Aircraft</t>
   </si>
@@ -80,10 +80,6 @@
   </si>
   <si>
     <t>Test Table</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>·</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -181,12 +177,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -209,7 +202,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -548,576 +543,577 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="7">
+      <c r="B3" s="8">
         <v>75.67</v>
       </c>
-      <c r="D3" s="7">
+      <c r="C3" s="6">
         <v>75.67</v>
       </c>
-      <c r="E3" s="7">
+      <c r="D3" s="6">
         <v>75.67</v>
       </c>
-      <c r="F3" s="7">
+      <c r="E3" s="6">
         <v>75.67</v>
       </c>
-      <c r="G3" s="7">
+      <c r="F3" s="6">
         <v>75.67</v>
       </c>
-      <c r="H3" s="7">
+      <c r="G3" s="6">
         <v>75.67</v>
       </c>
-      <c r="I3" s="7">
+      <c r="H3" s="6">
         <v>75.67</v>
       </c>
-      <c r="J3" s="7">
+      <c r="I3" s="6">
         <v>75.67</v>
       </c>
-      <c r="K3" s="7">
+      <c r="J3" s="6">
         <v>75.67</v>
       </c>
-      <c r="L3" s="7">
+      <c r="K3" s="6">
         <v>75.67</v>
       </c>
+      <c r="L3" s="6">
+        <v>75.67</v>
+      </c>
       <c r="M3" s="7">
-        <v>73.989999999999995</v>
-      </c>
-      <c r="N3" s="8"/>
+        <f t="shared" ref="M3:M13" si="0">AVERAGE(B3:L3)</f>
+        <v>75.669999999999987</v>
+      </c>
+      <c r="N3" s="7"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>92.86</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>98.91</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>98.91</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <v>98.91</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <v>98.91</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>98.91</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <v>98.91</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <v>98.91</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <v>98.91</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="9">
         <v>98.91</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="9">
         <v>98.91</v>
       </c>
-      <c r="M4" s="8">
-        <f t="shared" ref="M4:M13" si="0">AVERAGE(B4:L4)</f>
+      <c r="M4" s="7">
+        <f t="shared" si="0"/>
         <v>98.359999999999985</v>
       </c>
-      <c r="N4" s="8">
+      <c r="N4" s="7">
         <f>AVERAGE(B4)</f>
         <v>92.86</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>72.239999999999995</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>72.239999999999995</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>87.35</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="9">
         <v>87.35</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <v>87.35</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <v>87.35</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="9">
         <v>87.35</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="9">
         <v>87.35</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="9">
         <v>87.35</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="9">
         <v>87.35</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="9">
         <v>87.35</v>
       </c>
-      <c r="M5" s="8">
-        <f t="shared" si="0"/>
+      <c r="M5" s="7">
+        <f>AVERAGE(B5:L5)</f>
         <v>84.602727272727279</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N5" s="7">
         <f>AVERAGE(B5:C5)</f>
         <v>72.239999999999995</v>
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>64.63</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>64.63</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>64.63</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <v>78.19</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>78.19</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <v>78.19</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <v>78.78</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="9">
         <v>78.78</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="9">
         <v>78.78</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="9">
         <v>78.78</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="9">
         <v>82.18</v>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="7">
         <f t="shared" si="0"/>
         <v>75.069090909090903</v>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="7">
         <f>AVERAGE(B6:D6)</f>
         <v>64.63</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>43.17</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>43.17</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>43.17</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>43.17</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <v>98.59</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <v>98.59</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <v>98.59</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="9">
         <v>98.59</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="9">
         <v>98.59</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="9">
         <v>98.59</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="9">
         <v>98.59</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M7" s="7">
         <f t="shared" si="0"/>
         <v>78.437272727272742</v>
       </c>
-      <c r="N7" s="8">
+      <c r="N7" s="7">
         <f>AVERAGE(B7:E7)</f>
         <v>43.17</v>
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>84.81</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>84.81</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>84.81</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>84.81</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>84.81</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>95.09</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <v>98.15</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="9">
         <v>98.15</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="9">
         <v>98.15</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="9">
         <v>98.15</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="9">
         <v>98.15</v>
       </c>
-      <c r="M8" s="8">
+      <c r="M8" s="7">
         <f t="shared" si="0"/>
         <v>91.808181818181808</v>
       </c>
-      <c r="N8" s="8">
+      <c r="N8" s="7">
         <f>AVERAGE(B8:F8)</f>
         <v>84.81</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>91.6</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>91.6</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>91.6</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>91.6</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>91.6</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="6">
         <v>89.92</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>93.05</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="9">
         <v>93.05</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="9">
         <v>92.43</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="9">
         <v>92.43</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="9">
         <v>92.43</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="7">
         <f t="shared" si="0"/>
         <v>91.937272727272727</v>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="7">
         <f>AVERAGE(B9:G9)</f>
         <v>91.32</v>
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>84.32</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>84.32</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>84.32</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>84.32</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <v>84.32</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="6">
         <v>84.32</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="6">
         <v>84.32</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="8">
         <v>98.79</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="9">
         <v>98.79</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="9">
         <v>98.79</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="9">
         <v>98.79</v>
       </c>
-      <c r="M10" s="8">
+      <c r="M10" s="7">
         <f t="shared" si="0"/>
         <v>89.581818181818164</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N10" s="7">
         <f>AVERAGE(B10:H10)</f>
         <v>84.320000000000007</v>
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>94.14</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>94.14</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>94.14</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>94.14</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>94.14</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="6">
         <v>94.14</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="6">
         <v>92.01</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="6">
         <v>92.01</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="8">
         <v>94.58</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="9">
         <v>94.58</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="9">
         <v>94.58</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="7">
         <f t="shared" si="0"/>
         <v>93.872727272727289</v>
       </c>
-      <c r="N11" s="8">
+      <c r="N11" s="7">
         <f>AVERAGE(B11:I11)</f>
         <v>93.607500000000002</v>
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>90.96</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>90.96</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>90.96</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <v>90.96</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>90.96</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="6">
         <v>90.96</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="6">
         <v>90.96</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="6">
         <v>90.96</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="6">
         <v>90.66</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="8">
         <v>94.65</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="9">
         <v>94.65</v>
       </c>
-      <c r="M12" s="8">
+      <c r="M12" s="7">
         <f t="shared" si="0"/>
         <v>91.603636363636369</v>
       </c>
-      <c r="N12" s="8">
+      <c r="N12" s="7">
         <f>AVERAGE(B12:F12)</f>
         <v>90.96</v>
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>68.41</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <v>68.41</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>68.41</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <v>68.41</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <v>68.41</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="6">
         <v>68.41</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="6">
         <v>68.41</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="6">
         <v>68.41</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="6">
         <v>51.33</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="6">
         <v>51.33</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="8">
         <v>77.08</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M13" s="7">
         <f t="shared" si="0"/>
         <v>66.092727272727274</v>
       </c>
-      <c r="N13" s="8">
+      <c r="N13" s="7">
         <f>AVERAGE(B13:K13)</f>
         <v>64.994</v>
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="L14" s="8">
+      <c r="L14" s="7">
         <f>AVERAGE(L3:L13)</f>
         <v>90.761818181818185</v>
       </c>
-      <c r="M14" s="8">
+      <c r="M14" s="7">
         <f>AVERAGE(M3:M13)</f>
-        <v>85.032314049586773</v>
-      </c>
-      <c r="N14" s="8">
+        <v>85.185041322314063</v>
+      </c>
+      <c r="N14" s="7">
         <f>AVERAGE(N4:N13)</f>
         <v>78.291150000000002</v>
       </c>
